--- a/artfynd/A 61761-2024 artfynd.xlsx
+++ b/artfynd/A 61761-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135827006</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135827004</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135827005</v>
       </c>
       <c r="B4" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61761-2024 artfynd.xlsx
+++ b/artfynd/A 61761-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135827006</v>
       </c>
       <c r="B2" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135827005</v>
       </c>
       <c r="B4" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61761-2024 artfynd.xlsx
+++ b/artfynd/A 61761-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135827006</v>
       </c>
       <c r="B2" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135827004</v>
       </c>
       <c r="B3" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135827005</v>
       </c>
       <c r="B4" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61761-2024 artfynd.xlsx
+++ b/artfynd/A 61761-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135827006</v>
       </c>
       <c r="B2" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135827004</v>
       </c>
       <c r="B3" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135827005</v>
       </c>
       <c r="B4" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61761-2024 artfynd.xlsx
+++ b/artfynd/A 61761-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135827006</v>
       </c>
       <c r="B2" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135827004</v>
       </c>
       <c r="B3" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135827005</v>
       </c>
       <c r="B4" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61761-2024 artfynd.xlsx
+++ b/artfynd/A 61761-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135827006</v>
       </c>
       <c r="B2" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135827005</v>
       </c>
       <c r="B4" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61761-2024 artfynd.xlsx
+++ b/artfynd/A 61761-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135827006</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135827004</v>
       </c>
       <c r="B3" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135827005</v>
       </c>
       <c r="B4" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61761-2024 artfynd.xlsx
+++ b/artfynd/A 61761-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135827006</v>
       </c>
       <c r="B2" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135827004</v>
       </c>
       <c r="B3" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135827005</v>
       </c>
       <c r="B4" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
